--- a/outputs/metrics/baseline_final_test_metrics_with_validation_threshold.xlsx
+++ b/outputs/metrics/baseline_final_test_metrics_with_validation_threshold.xlsx
@@ -610,40 +610,40 @@
         <v>0.5</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7312703583061889</v>
+        <v>0.7214983713355049</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6788321167883211</v>
+        <v>0.6678832116788321</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7072243346007605</v>
+        <v>0.6958174904942965</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3211678832116788</v>
+        <v>0.3321167883211679</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6927374301675978</v>
+        <v>0.6815642458100558</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7492877492877493</v>
+        <v>0.7407407407407407</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5299145299145299</v>
+        <v>0.5169491525423728</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7971087495802325</v>
+        <v>0.7962421327440339</v>
       </c>
       <c r="L4" t="n">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M4" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="N4" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="O4" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5">
@@ -964,43 +964,43 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7052117263843648</v>
+        <v>0.7100977198697068</v>
       </c>
       <c r="E11" t="n">
-        <v>0.615819209039548</v>
+        <v>0.6197183098591549</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8288973384030418</v>
+        <v>0.8365019011406845</v>
       </c>
       <c r="G11" t="n">
-        <v>0.384180790960452</v>
+        <v>0.3802816901408451</v>
       </c>
       <c r="H11" t="n">
-        <v>0.706645056726094</v>
+        <v>0.7119741100323624</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6125356125356125</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5463659147869674</v>
+        <v>0.5527638190954773</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7971087495802325</v>
+        <v>0.7962421327440339</v>
       </c>
       <c r="L11" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N11" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="O11" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12">
@@ -1015,43 +1015,43 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7052117263843648</v>
+        <v>0.7100977198697068</v>
       </c>
       <c r="E12" t="n">
-        <v>0.615819209039548</v>
+        <v>0.6197183098591549</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8288973384030418</v>
+        <v>0.8365019011406845</v>
       </c>
       <c r="G12" t="n">
-        <v>0.384180790960452</v>
+        <v>0.3802816901408451</v>
       </c>
       <c r="H12" t="n">
-        <v>0.706645056726094</v>
+        <v>0.7119741100323624</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6125356125356125</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5463659147869674</v>
+        <v>0.5527638190954773</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7971087495802325</v>
+        <v>0.7962421327440339</v>
       </c>
       <c r="L12" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M12" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N12" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="O12" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13">
@@ -1066,43 +1066,43 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7328990228013029</v>
+        <v>0.7280130293159609</v>
       </c>
       <c r="E13" t="n">
-        <v>0.671280276816609</v>
+        <v>0.6632653061224489</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7376425855513308</v>
+        <v>0.7414448669201521</v>
       </c>
       <c r="G13" t="n">
-        <v>0.328719723183391</v>
+        <v>0.336734693877551</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7028985507246377</v>
+        <v>0.7001795332136446</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7293447293447294</v>
+        <v>0.717948717948718</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5418994413407822</v>
+        <v>0.5386740331491713</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7971087495802325</v>
+        <v>0.7962421327440339</v>
       </c>
       <c r="L13" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="M13" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="N13" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O13" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
